--- a/data/deliveryrate_by_snr/DR_by_SNR.xlsx
+++ b/data/deliveryrate_by_snr/DR_by_SNR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Jon/usra2026/data/deliveryrate_by_snr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D62E5F5B-C35C-CF4F-AA39-2C4D63500C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76F7FBB3-2244-0448-A3F7-7DB4E815D2A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{9C4A5E01-F19F-A04C-B214-4175DAF7C632}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="1" xr2:uid="{9C4A5E01-F19F-A04C-B214-4175DAF7C632}"/>
   </bookViews>
   <sheets>
     <sheet name="All Paths" sheetId="2" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2786" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2775" uniqueCount="119">
   <si>
     <t>Average SNR</t>
   </si>
@@ -466,25 +466,40 @@
     <t>1.32 (GB window)</t>
   </si>
   <si>
-    <t>Occurances to McCain</t>
-  </si>
-  <si>
-    <t>36.84 (McCain)</t>
-  </si>
-  <si>
     <t>71.05 (McCain)</t>
   </si>
   <si>
-    <t>30.136 (LSC Biology), 75 (rowe), 36.84 (McCain)</t>
+    <t>36.84 (McCain), 9.21 (James Dunn)</t>
   </si>
   <si>
-    <t>30.137 (LSC Biology), 75 (rowe), 77.63 (GB window), 2.64(McCain)</t>
+    <t>30.136 (LSC Biology), 75 (rowe), 36.84 (McCain), 9.21 (James Dunn)</t>
   </si>
   <si>
-    <t>2.63 (McCain)</t>
+    <t>30.137 (LSC Biology), 75 (rowe), 77.63 (GB window), 2.64(McCain), 5.26 (James Dunn)</t>
   </si>
   <si>
-    <t>1.32 (GB window), 36.84 (</t>
+    <t>2.63 (McCain), 5.26 (McCain)</t>
+  </si>
+  <si>
+    <t>5.26 (James Dunn)</t>
+  </si>
+  <si>
+    <t>18.42 (James Dunn)</t>
+  </si>
+  <si>
+    <t>1.32 (GB window), 36.84 (McCain), 9.21 (James Dunn)</t>
+  </si>
+  <si>
+    <t>14.47 (James Dunn)</t>
+  </si>
+  <si>
+    <t>1.32 (James Dunn)</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>Reliability-weighted mean hop distance</t>
   </si>
 </sst>
 </file>
@@ -539,7 +554,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -775,44 +790,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color theme="2" tint="-9.9978637043366805E-2"/>
-      </left>
-      <right style="thin">
-        <color theme="2" tint="-9.9978637043366805E-2"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="2" tint="-9.9978637043366805E-2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="2" tint="-9.9978637043366805E-2"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="2" tint="-9.9978637043366805E-2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="2" tint="-9.9978637043366805E-2"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -858,17 +840,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1689,7 +1665,7 @@
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A11" s="47" t="s">
+      <c r="A11" s="45" t="s">
         <v>70</v>
       </c>
       <c r="B11" t="s">
@@ -1726,7 +1702,7 @@
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="47" t="s">
         <v>95</v>
       </c>
       <c r="B12" t="s">
@@ -1758,10 +1734,12 @@
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
-      <c r="P12" s="21"/>
+      <c r="P12" s="21" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A13" s="47" t="s">
+      <c r="A13" s="45" t="s">
         <v>95</v>
       </c>
       <c r="B13" t="s">
@@ -1788,12 +1766,14 @@
       <c r="I13">
         <v>7</v>
       </c>
-      <c r="J13" s="53"/>
-      <c r="K13" s="53"/>
-      <c r="L13" s="53"/>
-      <c r="M13" s="53"/>
-      <c r="N13" s="53"/>
-      <c r="P13" s="21"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="P13" s="21" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -1832,7 +1812,7 @@
         <v>101</v>
       </c>
       <c r="P14" s="21" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q14">
         <v>-19.27840909</v>
@@ -1875,11 +1855,11 @@
         <v>99</v>
       </c>
       <c r="P15" s="44" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A16" s="47" t="s">
+      <c r="A16" s="45" t="s">
         <v>26</v>
       </c>
       <c r="B16" t="s">
@@ -1911,7 +1891,9 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-      <c r="P16" s="55"/>
+      <c r="P16" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
@@ -1949,7 +1931,7 @@
       <c r="O17" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="P17" s="54" t="s">
+      <c r="P17" s="48" t="s">
         <v>108</v>
       </c>
     </row>
@@ -1986,7 +1968,9 @@
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
-      <c r="P18" s="22"/>
+      <c r="P18" s="22" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" s="31" t="s">
@@ -2025,11 +2009,11 @@
         <v>100</v>
       </c>
       <c r="P19" s="21" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A20" s="48" t="s">
+      <c r="A20" s="46" t="s">
         <v>29</v>
       </c>
       <c r="B20" t="s">
@@ -2058,7 +2042,7 @@
       </c>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
-      <c r="L20" s="53"/>
+      <c r="L20" s="3"/>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
       <c r="O20" t="s">
@@ -2072,7 +2056,7 @@
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A21" s="48" t="s">
+      <c r="A21" s="46" t="s">
         <v>29</v>
       </c>
       <c r="B21" t="s">
@@ -2108,14 +2092,14 @@
         <v>103</v>
       </c>
       <c r="P21" s="21" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Q21">
         <v>-14.232954550000001</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A22" s="48" t="s">
+      <c r="A22" s="46" t="s">
         <v>29</v>
       </c>
       <c r="B22" t="s">
@@ -2158,7 +2142,7 @@
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A23" s="48" t="s">
+      <c r="A23" s="46" t="s">
         <v>29</v>
       </c>
       <c r="B23" t="s">
@@ -2194,7 +2178,7 @@
         <v>102</v>
       </c>
       <c r="P23" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.2">
@@ -2204,19 +2188,19 @@
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
       <c r="N24" s="5"/>
-      <c r="O24" t="s">
+      <c r="O24" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="P24" t="s">
+      <c r="P24" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="Q24" t="s">
+      <c r="Q24" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="R24" t="s">
+      <c r="R24" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="S24" t="s">
+      <c r="S24" s="1" t="s">
         <v>63</v>
       </c>
     </row>
@@ -2227,8 +2211,21 @@
       <c r="L25" s="5"/>
       <c r="M25" s="5"/>
       <c r="N25" s="5"/>
-      <c r="R25" s="44"/>
-      <c r="S25" s="44"/>
+      <c r="O25" t="s">
+        <v>26</v>
+      </c>
+      <c r="P25" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" s="31"/>
@@ -2241,10 +2238,10 @@
       <c r="Q26">
         <v>7</v>
       </c>
-      <c r="R26" s="44">
+      <c r="R26">
         <v>46.666666666666664</v>
       </c>
-      <c r="S26" s="44">
+      <c r="S26">
         <v>9.2105263157894726</v>
       </c>
     </row>
@@ -2258,10 +2255,10 @@
       <c r="Q27">
         <v>7</v>
       </c>
-      <c r="R27" s="44">
+      <c r="R27">
         <v>46.666666666666664</v>
       </c>
-      <c r="S27" s="44">
+      <c r="S27">
         <v>9.2105263157894726</v>
       </c>
     </row>
@@ -2275,23 +2272,49 @@
       <c r="Q28">
         <v>4</v>
       </c>
-      <c r="R28" s="44">
+      <c r="R28">
         <v>26.666666666666668</v>
       </c>
-      <c r="S28" s="44">
+      <c r="S28">
         <v>5.2631578947368416</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="R29" s="44"/>
-      <c r="S29" s="44"/>
+      <c r="O29" t="s">
+        <v>29</v>
+      </c>
+      <c r="P29" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="R30" s="44"/>
-      <c r="S30" s="44"/>
+      <c r="O30" t="s">
+        <v>70</v>
+      </c>
+      <c r="P30" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="O31" t="s">
+      <c r="O31" s="31" t="s">
         <v>29</v>
       </c>
       <c r="P31" t="s">
@@ -2300,15 +2323,15 @@
       <c r="Q31">
         <v>4</v>
       </c>
-      <c r="R31" s="44">
+      <c r="R31">
         <v>26.666666666666668</v>
       </c>
-      <c r="S31" s="44">
+      <c r="S31">
         <v>5.2631578947368416</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="O32" t="s">
+      <c r="O32" s="31" t="s">
         <v>18</v>
       </c>
       <c r="P32" t="s">
@@ -2317,15 +2340,15 @@
       <c r="Q32">
         <v>4</v>
       </c>
-      <c r="R32" s="44">
+      <c r="R32">
         <v>26.666666666666668</v>
       </c>
-      <c r="S32" s="44">
+      <c r="S32">
         <v>5.2631578947368416</v>
       </c>
     </row>
     <row r="33" spans="8:19" x14ac:dyDescent="0.2">
-      <c r="O33" t="s">
+      <c r="O33" s="37" t="s">
         <v>95</v>
       </c>
       <c r="P33" t="s">
@@ -2334,15 +2357,15 @@
       <c r="Q33">
         <v>14</v>
       </c>
-      <c r="R33" s="44">
+      <c r="R33">
         <v>93.333333333333329</v>
       </c>
-      <c r="S33" s="44">
+      <c r="S33">
         <v>18.421052631578945</v>
       </c>
     </row>
     <row r="34" spans="8:19" x14ac:dyDescent="0.2">
-      <c r="O34" t="s">
+      <c r="O34" s="31" t="s">
         <v>18</v>
       </c>
       <c r="P34" t="s">
@@ -2351,15 +2374,15 @@
       <c r="Q34">
         <v>7</v>
       </c>
-      <c r="R34" s="44">
+      <c r="R34">
         <v>46.666666666666664</v>
       </c>
-      <c r="S34" s="44">
+      <c r="S34">
         <v>9.2105263157894726</v>
       </c>
     </row>
     <row r="35" spans="8:19" x14ac:dyDescent="0.2">
-      <c r="O35" t="s">
+      <c r="O35" s="31" t="s">
         <v>26</v>
       </c>
       <c r="P35" t="s">
@@ -2368,16 +2391,29 @@
       <c r="Q35">
         <v>11</v>
       </c>
-      <c r="R35" s="44">
+      <c r="R35">
         <v>73.333333333333329</v>
       </c>
-      <c r="S35" s="44">
+      <c r="S35">
         <v>14.473684210526317</v>
       </c>
     </row>
     <row r="36" spans="8:19" x14ac:dyDescent="0.2">
-      <c r="R36" s="44"/>
-      <c r="S36" s="44"/>
+      <c r="O36" t="s">
+        <v>70</v>
+      </c>
+      <c r="P36" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
     </row>
     <row r="37" spans="8:19" x14ac:dyDescent="0.2">
       <c r="O37" t="s">
@@ -2389,274 +2425,72 @@
       <c r="Q37">
         <v>1</v>
       </c>
-      <c r="R37" s="44">
+      <c r="R37">
         <v>6.666666666666667</v>
       </c>
-      <c r="S37" s="44">
+      <c r="S37">
         <v>1.3157894736842104</v>
       </c>
     </row>
     <row r="40" spans="8:19" x14ac:dyDescent="0.2">
-      <c r="O40" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="P40" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q40" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="R40" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="S40" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="41" spans="8:19" x14ac:dyDescent="0.2">
-      <c r="O41" t="s">
-        <v>26</v>
-      </c>
-      <c r="P41" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q41">
-        <v>54</v>
-      </c>
-      <c r="R41">
-        <v>96.428571428571431</v>
-      </c>
-      <c r="S41">
-        <v>71.05263157894737</v>
-      </c>
+      <c r="O40" s="1"/>
+      <c r="P40" s="1"/>
+      <c r="Q40" s="1"/>
+      <c r="R40" s="1"/>
+      <c r="S40" s="1"/>
     </row>
     <row r="42" spans="8:19" x14ac:dyDescent="0.2">
       <c r="H42" s="44"/>
       <c r="I42" s="44"/>
-      <c r="O42" t="s">
-        <v>18</v>
-      </c>
-      <c r="P42" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q42">
-        <v>28</v>
-      </c>
-      <c r="R42">
-        <v>50</v>
-      </c>
-      <c r="S42">
-        <v>36.84210526315789</v>
-      </c>
     </row>
     <row r="43" spans="8:19" x14ac:dyDescent="0.2">
       <c r="H43" s="44"/>
       <c r="I43" s="44"/>
-      <c r="O43" t="s">
-        <v>29</v>
-      </c>
-      <c r="P43" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q43">
-        <v>28</v>
-      </c>
-      <c r="R43">
-        <v>50</v>
-      </c>
-      <c r="S43">
-        <v>36.84210526315789</v>
-      </c>
     </row>
     <row r="44" spans="8:19" x14ac:dyDescent="0.2">
       <c r="H44" s="44"/>
       <c r="I44" s="44"/>
-      <c r="O44" t="s">
-        <v>26</v>
-      </c>
-      <c r="P44" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q44">
-        <v>2</v>
-      </c>
-      <c r="R44">
-        <v>3.5714285714285712</v>
-      </c>
-      <c r="S44">
-        <v>2.6315789473684208</v>
-      </c>
     </row>
     <row r="45" spans="8:19" x14ac:dyDescent="0.2">
       <c r="H45" s="44"/>
       <c r="I45" s="44"/>
-      <c r="O45" t="s">
-        <v>29</v>
-      </c>
-      <c r="P45" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q45">
-        <v>0</v>
-      </c>
-      <c r="R45">
-        <v>0</v>
-      </c>
-      <c r="S45">
-        <v>0</v>
-      </c>
     </row>
     <row r="46" spans="8:19" x14ac:dyDescent="0.2">
       <c r="H46" s="44"/>
       <c r="I46" s="44"/>
-      <c r="O46" t="s">
-        <v>70</v>
-      </c>
-      <c r="P46" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q46">
-        <v>0</v>
-      </c>
-      <c r="R46">
-        <v>0</v>
-      </c>
-      <c r="S46">
-        <v>0</v>
-      </c>
     </row>
     <row r="47" spans="8:19" x14ac:dyDescent="0.2">
       <c r="H47" s="44"/>
       <c r="I47" s="44"/>
-      <c r="O47" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="P47" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q47">
-        <v>2</v>
-      </c>
-      <c r="R47">
-        <v>3.5714285714285712</v>
-      </c>
-      <c r="S47">
-        <v>2.6315789473684208</v>
-      </c>
+      <c r="O47" s="31"/>
     </row>
     <row r="48" spans="8:19" x14ac:dyDescent="0.2">
       <c r="H48" s="44"/>
       <c r="I48" s="44"/>
-      <c r="O48" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="P48" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q48">
-        <v>0</v>
-      </c>
-      <c r="R48">
-        <v>0</v>
-      </c>
-      <c r="S48">
-        <v>0</v>
-      </c>
+      <c r="O48" s="31"/>
     </row>
     <row r="49" spans="8:19" x14ac:dyDescent="0.2">
       <c r="H49" s="44"/>
       <c r="I49" s="44"/>
-      <c r="O49" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="P49" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q49">
-        <v>0</v>
-      </c>
-      <c r="R49">
-        <v>0</v>
-      </c>
-      <c r="S49">
-        <v>0</v>
-      </c>
+      <c r="O49" s="37"/>
     </row>
     <row r="50" spans="8:19" x14ac:dyDescent="0.2">
       <c r="H50" s="44"/>
       <c r="I50" s="44"/>
-      <c r="O50" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="P50" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q50">
-        <v>28</v>
-      </c>
-      <c r="R50">
-        <v>50</v>
-      </c>
-      <c r="S50">
-        <v>36.84210526315789</v>
-      </c>
+      <c r="O50" s="31"/>
     </row>
     <row r="51" spans="8:19" x14ac:dyDescent="0.2">
       <c r="H51" s="44"/>
       <c r="I51" s="44"/>
-      <c r="O51" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="P51" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q51">
-        <v>0</v>
-      </c>
-      <c r="R51">
-        <v>0</v>
-      </c>
-      <c r="S51">
-        <v>0</v>
-      </c>
+      <c r="O51" s="31"/>
     </row>
     <row r="52" spans="8:19" x14ac:dyDescent="0.2">
       <c r="H52" s="44"/>
       <c r="I52" s="44"/>
-      <c r="O52" t="s">
-        <v>70</v>
-      </c>
-      <c r="P52" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q52">
-        <v>0</v>
-      </c>
-      <c r="R52">
-        <v>0</v>
-      </c>
-      <c r="S52">
-        <v>0</v>
-      </c>
     </row>
     <row r="53" spans="8:19" x14ac:dyDescent="0.2">
       <c r="H53" s="44"/>
       <c r="I53" s="44"/>
-      <c r="O53" t="s">
-        <v>95</v>
-      </c>
-      <c r="P53" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q53">
-        <v>0</v>
-      </c>
-      <c r="R53">
-        <v>0</v>
-      </c>
-      <c r="S53">
-        <v>0</v>
-      </c>
     </row>
     <row r="54" spans="8:19" x14ac:dyDescent="0.2">
       <c r="H54" s="44"/>
@@ -16885,6 +16719,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -18780,11 +18615,11 @@
         <v>28</v>
       </c>
       <c r="I41">
-        <f t="shared" si="5"/>
+        <f>H41/$J$3*100</f>
         <v>50</v>
       </c>
       <c r="J41">
-        <f t="shared" si="6"/>
+        <f>H41/76*100</f>
         <v>36.84210526315789</v>
       </c>
     </row>
@@ -35569,10 +35404,15 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8E29A86-E86F-044C-A034-FFE299056A88}">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="73.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="26" t="s">
         <v>22</v>
       </c>
@@ -35582,254 +35422,375 @@
       <c r="C1" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
+      <c r="D1" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" s="49" t="s">
+        <v>117</v>
+      </c>
+      <c r="F1" s="49" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="27">
+      <c r="C2">
         <v>111.57</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="27" t="s">
+      <c r="D2" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2" cm="1">
+        <f t="array" ref="E2">_xlfn.LET(_xlpm.x,_xlfn.TEXTSPLIT(D2,","),_xlpm.p,--TRIM(_xlfn.TEXTBEFORE(_xlpm.x,"("))/100,SUM(_xlpm.p^2))</f>
+        <v>0.71353425130000014</v>
+      </c>
+      <c r="F2">
+        <f>SUMPRODUCT(C2:C16,E2:E16)/SUM(E2:E16)</f>
+        <v>260.01247183319862</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C3">
         <v>90.54</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
+      <c r="D3" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="E3" cm="1">
+        <f t="array" ref="E3">_xlfn.LET(_xlpm.x,_xlfn.TEXTSPLIT(D3,","),_xlpm.p,--TRIM(_xlfn.TEXTBEFORE(_xlpm.x,"("))/100,SUM(_xlpm.p^2))</f>
+        <v>0.58247423999999981</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4">
         <v>210.89</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="38" t="s">
+      <c r="D4" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="E4" cm="1">
+        <f t="array" ref="E4">_xlfn.LET(_xlpm.x,_xlfn.TEXTSPLIT(D4,","),_xlpm.p,--TRIM(_xlfn.TEXTBEFORE(_xlpm.x,"("))/100,SUM(_xlpm.p^2))</f>
+        <v>1.7423999999999999E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="47" t="s">
         <v>95</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5">
         <v>250.98</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
+      <c r="D5" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="E5" cm="1">
+        <f t="array" ref="E5">_xlfn.LET(_xlpm.x,_xlfn.TEXTSPLIT(D5,","),_xlpm.p,--TRIM(_xlfn.TEXTBEFORE(_xlpm.x,"("))/100,SUM(_xlpm.p^2))</f>
+        <v>3.3929640000000011E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6">
         <v>152.76</v>
       </c>
-      <c r="D6" s="51"/>
-      <c r="E6" s="27"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="27" t="s">
+      <c r="D6" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="E6" cm="1">
+        <f t="array" ref="E6">_xlfn.LET(_xlpm.x,_xlfn.TEXTSPLIT(D6,","),_xlpm.p,--TRIM(_xlfn.TEXTBEFORE(_xlpm.x,"("))/100,SUM(_xlpm.p^2))</f>
+        <v>1.7423999999999999E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="27">
-        <v>445.69</v>
-      </c>
-      <c r="D7" s="31"/>
-      <c r="E7" s="46"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="27" t="s">
+      <c r="C7">
+        <v>442.14</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="E7" cm="1">
+        <f t="array" ref="E7">_xlfn.LET(_xlpm.x,_xlfn.TEXTSPLIT(D7,","),_xlpm.p,--TRIM(_xlfn.TEXTBEFORE(_xlpm.x,"("))/100,SUM(_xlpm.p^2))</f>
+        <v>1.2594292869000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8">
+        <v>343.62</v>
+      </c>
+      <c r="D8" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="E8" cm="1">
+        <f t="array" ref="E8">_xlfn.LET(_xlpm.x,_xlfn.TEXTSPLIT(D8,","),_xlpm.p,--TRIM(_xlfn.TEXTBEFORE(_xlpm.x,"("))/100,SUM(_xlpm.p^2))</f>
+        <v>0.50481025000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C9">
+        <v>152.76</v>
+      </c>
+      <c r="D9" t="s">
+        <v>115</v>
+      </c>
+      <c r="E9" cm="1">
+        <f t="array" ref="E9">_xlfn.LET(_xlpm.x,_xlfn.TEXTSPLIT(D9,","),_xlpm.p,--TRIM(_xlfn.TEXTBEFORE(_xlpm.x,"("))/100,SUM(_xlpm.p^2))</f>
+        <v>2.0938089999999999E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C10">
+        <v>138.69999999999999</v>
+      </c>
+      <c r="D10" s="48" t="s">
+        <v>108</v>
+      </c>
+      <c r="E10" cm="1">
+        <f t="array" ref="E10">_xlfn.LET(_xlpm.x,_xlfn.TEXTSPLIT(D10,","),_xlpm.p,--TRIM(_xlfn.TEXTBEFORE(_xlpm.x,"("))/100,SUM(_xlpm.p^2))</f>
+        <v>0.14420097000000004</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11">
+        <v>250.98</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="E11" cm="1">
+        <f t="array" ref="E11">_xlfn.LET(_xlpm.x,_xlfn.TEXTSPLIT(D11,","),_xlpm.p,--TRIM(_xlfn.TEXTBEFORE(_xlpm.x,"("))/100,SUM(_xlpm.p^2))</f>
+        <v>2.7667600000000001E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12">
+        <v>343.62</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="E12" cm="1">
+        <f t="array" ref="E12">_xlfn.LET(_xlpm.x,_xlfn.TEXTSPLIT(D12,","),_xlpm.p,--TRIM(_xlfn.TEXTBEFORE(_xlpm.x,"("))/100,SUM(_xlpm.p^2))</f>
+        <v>0.14437521000000003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13">
+        <v>111.57</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="E13" cm="1">
+        <f t="array" ref="E13">_xlfn.LET(_xlpm.x,_xlfn.TEXTSPLIT(D13,","),_xlpm.p,--TRIM(_xlfn.TEXTBEFORE(_xlpm.x,"("))/100,SUM(_xlpm.p^2))</f>
+        <v>0.68416978900000003</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14">
         <v>442.14</v>
       </c>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="27" t="s">
+      <c r="D14" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" cm="1">
+        <f t="array" ref="E14">_xlfn.LET(_xlpm.x,_xlfn.TEXTSPLIT(D14,","),_xlpm.p,--TRIM(_xlfn.TEXTBEFORE(_xlpm.x,"("))/100,SUM(_xlpm.p^2))</f>
+        <v>0.79751881960000015</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15">
+        <v>90.54</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="E15" cm="1">
+        <f t="array" ref="E15">_xlfn.LET(_xlpm.x,_xlfn.TEXTSPLIT(D15,","),_xlpm.p,--TRIM(_xlfn.TEXTBEFORE(_xlpm.x,"("))/100,SUM(_xlpm.p^2))</f>
+        <v>0.60301461209999996</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="27">
-        <v>343.62</v>
-      </c>
-      <c r="D9" s="52"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="C10" s="27">
-        <v>152.76</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="27">
-        <v>369.88</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="27">
+      <c r="C16">
         <v>138.69999999999999</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="C13" s="27">
-        <v>250.98</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="27">
-        <v>343.62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="27">
-        <v>116.3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="27">
-        <v>148.15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="27" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="27">
-        <v>111.57</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="B18" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="27">
-        <v>442.14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="27" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" s="27">
-        <v>90.54</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="27">
-        <v>138.69999999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="27">
-        <v>109.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="50"/>
-      <c r="B22" s="27"/>
-      <c r="C22" s="27"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="41"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B24" s="27"/>
-      <c r="C24" s="27"/>
+      <c r="D16" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16" cm="1">
+        <f t="array" ref="E16">_xlfn.LET(_xlpm.x,_xlfn.TEXTSPLIT(D16,","),_xlpm.p,--TRIM(_xlfn.TEXTBEFORE(_xlpm.x,"("))/100,SUM(_xlpm.p^2))</f>
+        <v>3.4584500000000001E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17" s="27"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20" s="45"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A21" s="47"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A22" s="45"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="49"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="I23" s="21"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="I24" s="21"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" s="45"/>
+      <c r="F25" s="45"/>
+      <c r="I25" s="21"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="F26" s="47"/>
+      <c r="I26" s="21"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27" s="31"/>
+      <c r="F27" s="45"/>
+      <c r="I27" s="21"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28" s="31"/>
+      <c r="I28" s="21"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A29" s="46"/>
+      <c r="I29" s="44"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30" s="46"/>
+      <c r="F30" s="45"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A31" s="46"/>
+      <c r="I31" s="48"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A32" s="46"/>
+      <c r="F32" s="31"/>
+      <c r="I32" s="22"/>
+    </row>
+    <row r="33" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="F33" s="31"/>
+      <c r="I33" s="21"/>
+    </row>
+    <row r="34" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="F34" s="46"/>
+      <c r="I34" s="21"/>
+    </row>
+    <row r="35" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="F35" s="46"/>
+      <c r="I35" s="21"/>
+    </row>
+    <row r="36" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="F36" s="46"/>
+      <c r="I36" s="23"/>
+    </row>
+    <row r="37" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="F37" s="46"/>
+      <c r="I37" s="21"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C23">
     <sortCondition ref="A2:A23"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>